--- a/exports/data_base_lancar_19_07_2026.xlsx
+++ b/exports/data_base_lancar_19_07_2026.xlsx
@@ -2004,6 +2004,21 @@
       <c r="FD2" s="14" t="n"/>
       <c r="FE2" s="14" t="n"/>
       <c r="FF2" s="14" t="n"/>
+      <c r="FG2" t="inlineStr">
+        <is>
+          <t>ERRO</t>
+        </is>
+      </c>
+      <c r="FH2" t="inlineStr">
+        <is>
+          <t>19/07/2026 17:28:08</t>
+        </is>
+      </c>
+      <c r="FI2" t="inlineStr">
+        <is>
+          <t>Página Exame Físico não ficou verde; lote interrompido neste paciente.</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="23" customHeight="1">
       <c r="A3" t="inlineStr">
@@ -2356,6 +2371,21 @@
       <c r="FD3" s="14" t="n"/>
       <c r="FE3" s="14" t="n"/>
       <c r="FF3" s="14" t="n"/>
+      <c r="FG3" t="inlineStr">
+        <is>
+          <t>PRE_LANCADO</t>
+        </is>
+      </c>
+      <c r="FH3" t="inlineStr">
+        <is>
+          <t>19/07/2026 17:29:27</t>
+        </is>
+      </c>
+      <c r="FI3" t="inlineStr">
+        <is>
+          <t>Pré-lançamento preenchido e validado; aguardando confirmação.</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="23" customHeight="1">
       <c r="A4" t="inlineStr">
@@ -2606,6 +2636,21 @@
       <c r="FD4" s="14" t="n"/>
       <c r="FE4" s="14" t="n"/>
       <c r="FF4" s="14" t="n"/>
+      <c r="FG4" t="inlineStr">
+        <is>
+          <t>PRE_LANCADO</t>
+        </is>
+      </c>
+      <c r="FH4" t="inlineStr">
+        <is>
+          <t>19/07/2026 17:30:17</t>
+        </is>
+      </c>
+      <c r="FI4" t="inlineStr">
+        <is>
+          <t>Pré-lançamento preenchido e validado; aguardando confirmação.</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="23" customHeight="1">
       <c r="A5" t="inlineStr">
